--- a/top_resume_matches.xlsx
+++ b/top_resume_matches.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>filename</t>
   </si>
@@ -25,10 +25,16 @@
     <t>Govinda Gupta Resume .pdf</t>
   </si>
   <si>
+    <t>Kunal_CV_Python__.pdf</t>
+  </si>
+  <si>
+    <t>resume.pdf</t>
+  </si>
+  <si>
     <t>Tanisha_ Kumari.pdf</t>
   </si>
   <si>
-    <t>Kunal_CV_Python__.pdf</t>
+    <t>resume_AjayKushwaha.pdf</t>
   </si>
 </sst>
 </file>
@@ -386,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -402,7 +408,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.4099455074468649</v>
+        <v>0.4612119707427155</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -410,7 +416,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.3719164411625757</v>
+        <v>0.3541392117686383</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -418,7 +424,23 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.3036410676092735</v>
+        <v>0.3473442769762648</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0.317733808645857</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>0.30626633990065</v>
       </c>
     </row>
   </sheetData>
